--- a/input/mapping/074. OCB_GOLD_TCKH_TB_BCN085_THUNO_DTL_QUANG.xlsx
+++ b/input/mapping/074. OCB_GOLD_TCKH_TB_BCN085_THUNO_DTL_QUANG.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="274" documentId="11_7AAD4AA1A5384BEB4903E3E1C1AF8753CC7BDAD4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B26BBD0-FC94-441A-92D8-4C9F75889F86}"/>
+  <xr:revisionPtr revIDLastSave="277" documentId="11_7AAD4AA1A5384BEB4903E3E1C1AF8753CC7BDAD4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D73B2B1A-7D84-4BF9-8D54-4BAF5ADE6CFF}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -280,11 +280,9 @@
     WHERE  x.loans_payment_due_hashkey IS NULL
 ),
 stmt_hub AS (
-    SELECT stmt_entry_hashkey,
-           max_by(business_key, source_event_date) AS business_key
+    SELECT stmt_entry_hashkey, business_key
     FROM   IDENTIFIER(:cleaned || '.raw_vault.hub_stmt_entry')
     WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
-    GROUP BY stmt_entry_hashkey
 ),
 sat_stmt_info AS (
     SELECT stmt_entry_hashkey,
@@ -1306,59 +1304,59 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1731,7 +1729,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="33.950000000000003" customHeight="1">
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="44"/>
@@ -1746,392 +1744,392 @@
       <c r="L1" s="44"/>
     </row>
     <row r="3" spans="2:12">
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
       <c r="E3" s="11"/>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
     </row>
     <row r="4" spans="2:12">
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
       <c r="E4" s="11"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
     </row>
     <row r="5" spans="2:12">
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
       <c r="E5" s="11"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
     </row>
     <row r="6" spans="2:12" ht="50.25" customHeight="1">
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
       <c r="E6" s="11"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
       <c r="E7" s="11"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="2:12">
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
       <c r="E8" s="11"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="2:12" ht="63" customHeight="1">
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
       <c r="E9" s="11"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="2:12">
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
       <c r="E10" s="11"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
     </row>
     <row r="11" spans="2:12">
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
       <c r="E11" s="11"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
     </row>
     <row r="12" spans="2:12" ht="63" customHeight="1">
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
       <c r="E12" s="11"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
     </row>
     <row r="13" spans="2:12">
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
       <c r="E13" s="11"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
     </row>
     <row r="14" spans="2:12" ht="18.75">
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
       <c r="E14" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
     </row>
     <row r="15" spans="2:12" ht="75.75" customHeight="1">
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
       <c r="E15" s="11"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
     </row>
     <row r="16" spans="2:12">
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
       <c r="E16" s="11"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
       <c r="E17" s="11"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
     </row>
     <row r="18" spans="2:9" ht="43.5" customHeight="1">
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
       <c r="E18" s="11"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
       <c r="E19" s="11"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
       <c r="E20" s="11"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
     </row>
     <row r="21" spans="2:9" ht="57.75" customHeight="1">
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
       <c r="E21" s="11"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
       <c r="E22" s="11"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
       <c r="E23" s="11"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
       <c r="E24" s="11"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
       <c r="E25" s="11"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
       <c r="I25" s="10"/>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
       <c r="E26" s="11"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
     </row>
     <row r="27" spans="2:9" ht="18" customHeight="1">
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
     </row>
     <row r="28" spans="2:9" ht="18" customHeight="1">
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
       <c r="E28" s="11"/>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
     </row>
     <row r="29" spans="2:9" ht="18" customHeight="1">
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
       <c r="E29" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
     </row>
     <row r="30" spans="2:9" ht="18" customHeight="1">
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
       <c r="E30" s="11"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
     </row>
     <row r="31" spans="2:9" ht="18" customHeight="1">
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
       <c r="E33" s="11"/>
-      <c r="F33" s="30" t="s">
+      <c r="F33" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
       <c r="E34" s="11"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
     </row>
     <row r="35" spans="2:9" ht="18.75">
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
       <c r="E35" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="11"/>
       <c r="H38" s="11"/>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="30" t="s">
+      <c r="F39" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
     </row>
     <row r="40" spans="2:9" ht="18.75">
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
       <c r="E40" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
     </row>
     <row r="41" spans="2:9">
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
       <c r="E41" s="11"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
       <c r="E42" s="11"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
       <c r="E43" s="11"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
     </row>
     <row r="45" spans="2:9" ht="15.75">
       <c r="B45" s="18" t="s">
@@ -2146,64 +2144,64 @@
       <c r="I45" s="19"/>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="22"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="24" t="s">
+      <c r="B46" s="21"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="24"/>
-      <c r="I46" s="24"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="23"/>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="25"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="24" t="s">
+      <c r="B47" s="24"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="27"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="23"/>
+      <c r="I47" s="26"/>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="32"/>
-      <c r="C48" s="33"/>
-      <c r="D48" s="24" t="s">
+      <c r="B48" s="31"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="24"/>
-      <c r="I48" s="24"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="23"/>
+      <c r="G48" s="23"/>
+      <c r="H48" s="23"/>
+      <c r="I48" s="23"/>
     </row>
     <row r="49" spans="2:9">
-      <c r="B49" s="34"/>
-      <c r="C49" s="35"/>
-      <c r="D49" s="24" t="s">
+      <c r="B49" s="33"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="24"/>
-      <c r="I49" s="24"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="23"/>
     </row>
     <row r="50" spans="2:9">
-      <c r="B50" s="36"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="24" t="s">
+      <c r="B50" s="35"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="24"/>
-      <c r="I50" s="24"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="23"/>
+      <c r="I50" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2249,7 +2247,7 @@
       <c r="C1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="37" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="44"/>
@@ -3311,16 +3309,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -3492,7 +3480,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3501,14 +3489,24 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF0FBC26-7E30-4C4D-9CD6-2B55AD9D5B92}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F38680F-F532-4A5A-A549-757FA6242FF3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F38680F-F532-4A5A-A549-757FA6242FF3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA0B9CA2-9167-4689-9138-BF5F8581B774}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA0B9CA2-9167-4689-9138-BF5F8581B774}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF0FBC26-7E30-4C4D-9CD6-2B55AD9D5B92}"/>
 </file>